--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/29.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/29.xlsx
@@ -426,13 +426,13 @@
         <v>-11.17599138056864</v>
       </c>
       <c r="E2">
-        <v>-16.01673915206685</v>
+        <v>-17.2918849770427</v>
       </c>
       <c r="F2">
-        <v>-4.057280730236873</v>
+        <v>-4.575813044999877</v>
       </c>
       <c r="G2">
-        <v>-13.53130707721328</v>
+        <v>-13.8767721297102</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.60295755577129</v>
       </c>
       <c r="E3">
-        <v>-16.57897637096317</v>
+        <v>-16.61899902424296</v>
       </c>
       <c r="F3">
-        <v>-3.920407927537505</v>
+        <v>-3.740453392953341</v>
       </c>
       <c r="G3">
-        <v>-13.51043522687365</v>
+        <v>-13.9890145162049</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.97570490828671</v>
       </c>
       <c r="E4">
-        <v>-16.75312336740214</v>
+        <v>-17.76398744929035</v>
       </c>
       <c r="F4">
-        <v>-3.78838852945114</v>
+        <v>-3.622333999885951</v>
       </c>
       <c r="G4">
-        <v>-14.26581180451654</v>
+        <v>-14.11407499472158</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.23605532354034</v>
       </c>
       <c r="E5">
-        <v>-17.07859385128143</v>
+        <v>-17.1431698906308</v>
       </c>
       <c r="F5">
-        <v>-3.350092709690699</v>
+        <v>-3.344673530141585</v>
       </c>
       <c r="G5">
-        <v>-14.40169703295782</v>
+        <v>-13.64552968091911</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.39561407050222</v>
       </c>
       <c r="E6">
-        <v>-17.08219851659153</v>
+        <v>-18.49737834330657</v>
       </c>
       <c r="F6">
-        <v>-3.548375701429205</v>
+        <v>-3.59367000264688</v>
       </c>
       <c r="G6">
-        <v>-13.53452267434154</v>
+        <v>-13.70404698621025</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.46068707040065</v>
       </c>
       <c r="E7">
-        <v>-18.51934597071778</v>
+        <v>-17.9193458070715</v>
       </c>
       <c r="F7">
-        <v>-3.202514915044953</v>
+        <v>-3.165015551087623</v>
       </c>
       <c r="G7">
-        <v>-13.40418271033571</v>
+        <v>-12.72960949481571</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.44643299739318</v>
       </c>
       <c r="E8">
-        <v>-18.90297564627758</v>
+        <v>-20.73585738698612</v>
       </c>
       <c r="F8">
-        <v>-3.095225597401764</v>
+        <v>-3.250328281534541</v>
       </c>
       <c r="G8">
-        <v>-13.24215927095189</v>
+        <v>-13.24451846925313</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.37049477454175</v>
       </c>
       <c r="E9">
-        <v>-19.61006516325725</v>
+        <v>-20.17516437772642</v>
       </c>
       <c r="F9">
-        <v>-2.593828062365668</v>
+        <v>-2.612362783003307</v>
       </c>
       <c r="G9">
-        <v>-12.80197027386615</v>
+        <v>-12.09133643340785</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.24947443888602</v>
       </c>
       <c r="E10">
-        <v>-20.80507511219336</v>
+        <v>-20.30088840160137</v>
       </c>
       <c r="F10">
-        <v>-2.522728459815984</v>
+        <v>-2.445978563211804</v>
       </c>
       <c r="G10">
-        <v>-12.22121374517379</v>
+        <v>-13.86933688165649</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.09930607520873</v>
       </c>
       <c r="E11">
-        <v>-20.9005625151191</v>
+        <v>-22.45435893120893</v>
       </c>
       <c r="F11">
-        <v>-2.465751693116628</v>
+        <v>-2.254475758665211</v>
       </c>
       <c r="G11">
-        <v>-11.5705311038281</v>
+        <v>-12.00106018464285</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.93375452050518</v>
       </c>
       <c r="E12">
-        <v>-21.16679150203004</v>
+        <v>-21.48338164838028</v>
       </c>
       <c r="F12">
-        <v>-2.38509935767786</v>
+        <v>-2.320660657414086</v>
       </c>
       <c r="G12">
-        <v>-11.57166968770923</v>
+        <v>-12.66425412379469</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.76211278407841</v>
       </c>
       <c r="E13">
-        <v>-22.1968744276068</v>
+        <v>-24.05237589598366</v>
       </c>
       <c r="F13">
-        <v>-2.038457420832767</v>
+        <v>-2.05131202618941</v>
       </c>
       <c r="G13">
-        <v>-10.94378825498013</v>
+        <v>-10.68114287525438</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.5953246611239</v>
       </c>
       <c r="E14">
-        <v>-23.56980359183028</v>
+        <v>-25.08743561449485</v>
       </c>
       <c r="F14">
-        <v>-1.769266179414623</v>
+        <v>-1.649178585398182</v>
       </c>
       <c r="G14">
-        <v>-10.52519625819865</v>
+        <v>-11.14714196112671</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.43477781095607</v>
       </c>
       <c r="E15">
-        <v>-24.20237254053973</v>
+        <v>-24.42743769872094</v>
       </c>
       <c r="F15">
-        <v>-1.445767171068944</v>
+        <v>-1.531929806471134</v>
       </c>
       <c r="G15">
-        <v>-10.09705262545762</v>
+        <v>-10.34062098303676</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.28419396468203</v>
       </c>
       <c r="E16">
-        <v>-24.94502416390164</v>
+        <v>-24.47327944110059</v>
       </c>
       <c r="F16">
-        <v>-0.9918756782159965</v>
+        <v>-0.3522559299813723</v>
       </c>
       <c r="G16">
-        <v>-9.529453795218638</v>
+        <v>-10.05324831763904</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.13342831315428</v>
       </c>
       <c r="E17">
-        <v>-25.59713347795418</v>
+        <v>-25.85245789945465</v>
       </c>
       <c r="F17">
-        <v>-0.4643911969309386</v>
+        <v>-1.117068500535892</v>
       </c>
       <c r="G17">
-        <v>-9.103370769616944</v>
+        <v>-9.6757536208896</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.97774192291882</v>
       </c>
       <c r="E18">
-        <v>-26.72262682239855</v>
+        <v>-26.8579149833777</v>
       </c>
       <c r="F18">
-        <v>-0.4042310143026245</v>
+        <v>-0.410409806760106</v>
       </c>
       <c r="G18">
-        <v>-8.956473761622163</v>
+        <v>-9.151906598924249</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.79820599926909</v>
       </c>
       <c r="E19">
-        <v>-27.22296433008403</v>
+        <v>-28.54168313196168</v>
       </c>
       <c r="F19">
-        <v>-0.1018943079962637</v>
+        <v>-0.1002897603370411</v>
       </c>
       <c r="G19">
-        <v>-8.47543683734289</v>
+        <v>-9.051688248834131</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.58719071853081</v>
       </c>
       <c r="E20">
-        <v>-27.57310141188309</v>
+        <v>-26.97636627799633</v>
       </c>
       <c r="F20">
-        <v>0.2303961635953271</v>
+        <v>0.8877968181310428</v>
       </c>
       <c r="G20">
-        <v>-8.968355064888913</v>
+        <v>-9.088237775784785</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.32967897238956</v>
       </c>
       <c r="E21">
-        <v>-28.23992826646056</v>
+        <v>-28.64091558289176</v>
       </c>
       <c r="F21">
-        <v>0.310083451009834</v>
+        <v>0.4634449068619261</v>
       </c>
       <c r="G21">
-        <v>-8.562389208668174</v>
+        <v>-8.75334317854162</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.02859937702692</v>
       </c>
       <c r="E22">
-        <v>-29.88697728355335</v>
+        <v>-27.24930193491264</v>
       </c>
       <c r="F22">
-        <v>0.7125424401903626</v>
+        <v>0.8567148164431997</v>
       </c>
       <c r="G22">
-        <v>-8.772453012903826</v>
+        <v>-8.013778807593697</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.686146088194416</v>
       </c>
       <c r="E23">
-        <v>-29.61303404117034</v>
+        <v>-29.63161663426082</v>
       </c>
       <c r="F23">
-        <v>0.5308905807978618</v>
+        <v>1.399951532259893</v>
       </c>
       <c r="G23">
-        <v>-8.693979318088145</v>
+        <v>-9.012205309809332</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.320163075580334</v>
       </c>
       <c r="E24">
-        <v>-31.03975468389393</v>
+        <v>-29.05898430327989</v>
       </c>
       <c r="F24">
-        <v>0.6086071821611087</v>
+        <v>1.484319095500217</v>
       </c>
       <c r="G24">
-        <v>-7.987351849153929</v>
+        <v>-8.244025405641491</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.942715962528387</v>
       </c>
       <c r="E25">
-        <v>-30.27708946965512</v>
+        <v>-30.160123514511</v>
       </c>
       <c r="F25">
-        <v>0.651302066468798</v>
+        <v>0.9118526075083404</v>
       </c>
       <c r="G25">
-        <v>-8.972784713994162</v>
+        <v>-7.703161968668862</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.573155030238322</v>
       </c>
       <c r="E26">
-        <v>-30.67029460350414</v>
+        <v>-31.19114836268136</v>
       </c>
       <c r="F26">
-        <v>0.8260585956003956</v>
+        <v>1.290593781211914</v>
       </c>
       <c r="G26">
-        <v>-8.199646884050003</v>
+        <v>-9.078069270172065</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.224642296163422</v>
       </c>
       <c r="E27">
-        <v>-31.01046677824932</v>
+        <v>-30.51727973102196</v>
       </c>
       <c r="F27">
-        <v>0.6572033558463416</v>
+        <v>1.057297356091878</v>
       </c>
       <c r="G27">
-        <v>-8.004502794245147</v>
+        <v>-8.869413109985416</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.912924900826645</v>
       </c>
       <c r="E28">
-        <v>-30.2501541062575</v>
+        <v>-29.32411739948097</v>
       </c>
       <c r="F28">
-        <v>0.2501411290084561</v>
+        <v>0.8451938826050642</v>
       </c>
       <c r="G28">
-        <v>-8.270685330811979</v>
+        <v>-8.853486060535872</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.647506581334134</v>
       </c>
       <c r="E29">
-        <v>-30.18954727437584</v>
+        <v>-30.84200754516398</v>
       </c>
       <c r="F29">
-        <v>0.4823192581347128</v>
+        <v>0.604940828036318</v>
       </c>
       <c r="G29">
-        <v>-8.145437822666416</v>
+        <v>-8.903455783664656</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.4348838915451</v>
       </c>
       <c r="E30">
-        <v>-28.94555508633576</v>
+        <v>-29.40083427764491</v>
       </c>
       <c r="F30">
-        <v>0.1765489689437481</v>
+        <v>0.7722279682968726</v>
       </c>
       <c r="G30">
-        <v>-7.816482236445845</v>
+        <v>-9.093530386160168</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.277352974470387</v>
       </c>
       <c r="E31">
-        <v>-29.70974186784115</v>
+        <v>-27.56152663231948</v>
       </c>
       <c r="F31">
-        <v>-0.003297049510649784</v>
+        <v>0.3749230810965625</v>
       </c>
       <c r="G31">
-        <v>-7.390199056329025</v>
+        <v>-8.406409779396851</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.170203170337563</v>
       </c>
       <c r="E32">
-        <v>-29.6033317856089</v>
+        <v>-29.00477394093407</v>
       </c>
       <c r="F32">
-        <v>0.1004982144275311</v>
+        <v>0.8742795188521605</v>
       </c>
       <c r="G32">
-        <v>-8.438309815397773</v>
+        <v>-9.051622624402942</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.10817624426115</v>
       </c>
       <c r="E33">
-        <v>-28.61928759103112</v>
+        <v>-28.37388505608146</v>
       </c>
       <c r="F33">
-        <v>0.2941464905473743</v>
+        <v>0.5501434959737279</v>
       </c>
       <c r="G33">
-        <v>-7.783351742360132</v>
+        <v>-8.141818635286349</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.078313290734007</v>
       </c>
       <c r="E34">
-        <v>-28.3938012847672</v>
+        <v>-26.9561511700261</v>
       </c>
       <c r="F34">
-        <v>-0.3567158600780448</v>
+        <v>0.9514071509920168</v>
       </c>
       <c r="G34">
-        <v>-7.76338550917091</v>
+        <v>-8.984045866386177</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.071260760683323</v>
       </c>
       <c r="E35">
-        <v>-27.35435347494257</v>
+        <v>-27.86262486908949</v>
       </c>
       <c r="F35">
-        <v>-0.3073609018518475</v>
+        <v>0.6804763380279937</v>
       </c>
       <c r="G35">
-        <v>-6.892529619964926</v>
+        <v>-8.340293164974041</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.070622715492205</v>
       </c>
       <c r="E36">
-        <v>-27.36321117010158</v>
+        <v>-26.60994027519168</v>
       </c>
       <c r="F36">
-        <v>-0.1907822721536647</v>
+        <v>0.5121454548399118</v>
       </c>
       <c r="G36">
-        <v>-7.206447367778562</v>
+        <v>-8.695423055574301</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.066949566398285</v>
       </c>
       <c r="E37">
-        <v>-26.39851940919558</v>
+        <v>-26.34353014932043</v>
       </c>
       <c r="F37">
-        <v>-0.09914578495377498</v>
+        <v>0.1545367619491568</v>
       </c>
       <c r="G37">
-        <v>-7.37356982546576</v>
+        <v>-8.852646067816654</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.044842413501998</v>
       </c>
       <c r="E38">
-        <v>-26.90367974169922</v>
+        <v>-26.07420821466225</v>
       </c>
       <c r="F38">
-        <v>-0.2912615813784391</v>
+        <v>0.8048424496798947</v>
       </c>
       <c r="G38">
-        <v>-7.707191308743861</v>
+        <v>-8.074071253748492</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.999259497955399</v>
       </c>
       <c r="E39">
-        <v>-25.89862569196285</v>
+        <v>-25.13351736599691</v>
       </c>
       <c r="F39">
-        <v>-0.1102575052949275</v>
+        <v>0.5693094325723</v>
       </c>
       <c r="G39">
-        <v>-8.386414015213594</v>
+        <v>-7.326638513501022</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.922222034714977</v>
       </c>
       <c r="E40">
-        <v>-25.03303505624071</v>
+        <v>-24.72117263675447</v>
       </c>
       <c r="F40">
-        <v>0.06158234221141309</v>
+        <v>0.7936843407641854</v>
       </c>
       <c r="G40">
-        <v>-7.38692111599114</v>
+        <v>-8.096481996999501</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.816164474885102</v>
       </c>
       <c r="E41">
-        <v>-24.37852112249009</v>
+        <v>-23.85004367732095</v>
       </c>
       <c r="F41">
-        <v>0.1760502917672628</v>
+        <v>0.2984382620612785</v>
       </c>
       <c r="G41">
-        <v>-7.704628674705934</v>
+        <v>-8.740027981453393</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.67929524606591</v>
       </c>
       <c r="E42">
-        <v>-23.72286148481553</v>
+        <v>-23.31393575344889</v>
       </c>
       <c r="F42">
-        <v>0.06047978519828695</v>
+        <v>0.205875660105059</v>
       </c>
       <c r="G42">
-        <v>-7.182766791784049</v>
+        <v>-8.518670212610132</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.517911311952812</v>
       </c>
       <c r="E43">
-        <v>-22.42551708025408</v>
+        <v>-23.21703546663276</v>
       </c>
       <c r="F43">
-        <v>-0.301525053499125</v>
+        <v>0.2641802997511022</v>
       </c>
       <c r="G43">
-        <v>-7.761630055636608</v>
+        <v>-8.511497462281186</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.334081524586001</v>
       </c>
       <c r="E44">
-        <v>-22.48131240850259</v>
+        <v>-23.29853894182281</v>
       </c>
       <c r="F44">
-        <v>-0.02274628776097938</v>
+        <v>0.4945012291602823</v>
       </c>
       <c r="G44">
-        <v>-7.586156889080623</v>
+        <v>-7.956659302686883</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.136524684706125</v>
       </c>
       <c r="E45">
-        <v>-21.53455340466696</v>
+        <v>-21.89958916595126</v>
       </c>
       <c r="F45">
-        <v>-0.06225941287451579</v>
+        <v>-0.03701408790679806</v>
       </c>
       <c r="G45">
-        <v>-7.904543660658223</v>
+        <v>-7.842551541735634</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.930471780476414</v>
       </c>
       <c r="E46">
-        <v>-20.60898765918723</v>
+        <v>-22.52452310748378</v>
       </c>
       <c r="F46">
-        <v>-0.2478658982479814</v>
+        <v>0.06653100907573734</v>
       </c>
       <c r="G46">
-        <v>-8.285860980524411</v>
+        <v>-8.796802958096464</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.724891026369074</v>
       </c>
       <c r="E47">
-        <v>-20.75860391192665</v>
+        <v>-21.59504928893543</v>
       </c>
       <c r="F47">
-        <v>-0.1146097476292361</v>
+        <v>0.3712948318723007</v>
       </c>
       <c r="G47">
-        <v>-8.15675147460338</v>
+        <v>-8.319828186107783</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.525973999477053</v>
       </c>
       <c r="E48">
-        <v>-19.93487901840542</v>
+        <v>-20.36723507428775</v>
       </c>
       <c r="F48">
-        <v>-0.5840820029614392</v>
+        <v>0.5379747788266032</v>
       </c>
       <c r="G48">
-        <v>-7.95626555609975</v>
+        <v>-6.994053896235705</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.341069926365512</v>
       </c>
       <c r="E49">
-        <v>-19.1292816063369</v>
+        <v>-20.60547356335728</v>
       </c>
       <c r="F49">
-        <v>0.004656934291031069</v>
+        <v>-0.03181359735202276</v>
       </c>
       <c r="G49">
-        <v>-8.120051011460992</v>
+        <v>-7.716880756008901</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.174066816802364</v>
       </c>
       <c r="E50">
-        <v>-18.91390738253209</v>
+        <v>-19.20730721348906</v>
       </c>
       <c r="F50">
-        <v>-0.2966028943916904</v>
+        <v>0.05086243965178469</v>
       </c>
       <c r="G50">
-        <v>-8.183601710624316</v>
+        <v>-8.463227411920196</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.026877622732683</v>
       </c>
       <c r="E51">
-        <v>-18.90890794722763</v>
+        <v>-18.40359817508173</v>
       </c>
       <c r="F51">
-        <v>-0.3968353501304305</v>
+        <v>-0.3704882965169894</v>
       </c>
       <c r="G51">
-        <v>-7.921415701916887</v>
+        <v>-8.56809197173849</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.900761361862152</v>
       </c>
       <c r="E52">
-        <v>-18.21426267682103</v>
+        <v>-18.29643183769021</v>
       </c>
       <c r="F52">
-        <v>-0.303900811210354</v>
+        <v>-0.09792891323906251</v>
       </c>
       <c r="G52">
-        <v>-7.643722640119521</v>
+        <v>-7.951648877365611</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.794144984356415</v>
       </c>
       <c r="E53">
-        <v>-17.04435858778344</v>
+        <v>-18.55546960787697</v>
       </c>
       <c r="F53">
-        <v>-0.3620613149283101</v>
+        <v>-0.22817643345084</v>
       </c>
       <c r="G53">
-        <v>-8.345953272164083</v>
+        <v>-8.425378521232002</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.708248434801919</v>
       </c>
       <c r="E54">
-        <v>-16.90197430803427</v>
+        <v>-18.20307734602208</v>
       </c>
       <c r="F54">
-        <v>-0.3452495984884941</v>
+        <v>-0.3790271077050467</v>
       </c>
       <c r="G54">
-        <v>-8.194643021171849</v>
+        <v>-7.275211927999845</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.640937503242154</v>
       </c>
       <c r="E55">
-        <v>-16.29626826713832</v>
+        <v>-16.85398154050098</v>
       </c>
       <c r="F55">
-        <v>-0.7508083384902985</v>
+        <v>-0.7764405110351236</v>
       </c>
       <c r="G55">
-        <v>-8.524031728638265</v>
+        <v>-9.310881783479346</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.593219220190017</v>
       </c>
       <c r="E56">
-        <v>-16.37210209287077</v>
+        <v>-14.84433081690302</v>
       </c>
       <c r="F56">
-        <v>-0.4178941062443995</v>
+        <v>-0.6882251812087958</v>
       </c>
       <c r="G56">
-        <v>-8.217516416662738</v>
+        <v>-9.249385129012234</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.562944451193349</v>
       </c>
       <c r="E57">
-        <v>-15.40704352557015</v>
+        <v>-16.91316869578123</v>
       </c>
       <c r="F57">
-        <v>-0.5692061811419656</v>
+        <v>-0.4568124635627259</v>
       </c>
       <c r="G57">
-        <v>-9.378468385160788</v>
+        <v>-8.836482770414829</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.55330895955207</v>
       </c>
       <c r="E58">
-        <v>-14.85346474897649</v>
+        <v>-15.69514504193813</v>
       </c>
       <c r="F58">
-        <v>-0.2737697753009248</v>
+        <v>-0.02425474480147728</v>
       </c>
       <c r="G58">
-        <v>-9.29142085841028</v>
+        <v>-9.478637516927517</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.563972254167772</v>
       </c>
       <c r="E59">
-        <v>-13.88174026793658</v>
+        <v>-15.26018058502739</v>
       </c>
       <c r="F59">
-        <v>-0.6224619214679459</v>
+        <v>-0.4960911607012701</v>
       </c>
       <c r="G59">
-        <v>-9.213354035067971</v>
+        <v>-8.484666913589608</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.597746345143477</v>
       </c>
       <c r="E60">
-        <v>-13.64776307290826</v>
+        <v>-14.47217629447866</v>
       </c>
       <c r="F60">
-        <v>-0.6618052312639083</v>
+        <v>-0.544824015007965</v>
       </c>
       <c r="G60">
-        <v>-8.831321408901823</v>
+        <v>-8.817264655741162</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.651559242468308</v>
       </c>
       <c r="E61">
-        <v>-12.81304304449641</v>
+        <v>-15.85501375983092</v>
       </c>
       <c r="F61">
-        <v>-0.6444534192774671</v>
+        <v>-0.05195783585330115</v>
       </c>
       <c r="G61">
-        <v>-9.290918831511684</v>
+        <v>-9.109332749190454</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.725514849189098</v>
       </c>
       <c r="E62">
-        <v>-13.01121812402008</v>
+        <v>-14.05554310035096</v>
       </c>
       <c r="F62">
-        <v>-0.6981183731004303</v>
+        <v>0.4240113050190584</v>
       </c>
       <c r="G62">
-        <v>-9.213642782565202</v>
+        <v>-9.627496695414845</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.813888207511969</v>
       </c>
       <c r="E63">
-        <v>-13.57462368921038</v>
+        <v>-14.91431385421756</v>
       </c>
       <c r="F63">
-        <v>-1.039822411857435</v>
+        <v>-0.8683163964144224</v>
       </c>
       <c r="G63">
-        <v>-9.039790539459583</v>
+        <v>-9.025172697412257</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.914828028162673</v>
       </c>
       <c r="E64">
-        <v>-13.17057512435</v>
+        <v>-14.22616241553796</v>
       </c>
       <c r="F64">
-        <v>-0.9770818647694002</v>
+        <v>-0.4555823379695687</v>
       </c>
       <c r="G64">
-        <v>-9.209380475759483</v>
+        <v>-10.60251824424696</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.021650848691954</v>
       </c>
       <c r="E65">
-        <v>-12.20649017896103</v>
+        <v>-12.82284266224901</v>
       </c>
       <c r="F65">
-        <v>-1.017083726650588</v>
+        <v>-0.5313912092041682</v>
       </c>
       <c r="G65">
-        <v>-8.872759955976051</v>
+        <v>-10.90952902067797</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.131455649520469</v>
       </c>
       <c r="E66">
-        <v>-12.00739129073979</v>
+        <v>-11.82617081790084</v>
       </c>
       <c r="F66">
-        <v>-1.163549023874374</v>
+        <v>-0.2141215237275408</v>
       </c>
       <c r="G66">
-        <v>-9.091696183308439</v>
+        <v>-10.1087862737542</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.236456852359378</v>
       </c>
       <c r="E67">
-        <v>-12.51983793792178</v>
+        <v>-13.65298893191312</v>
       </c>
       <c r="F67">
-        <v>-1.01543610388642</v>
+        <v>-1.163105018946474</v>
       </c>
       <c r="G67">
-        <v>-8.842763028479606</v>
+        <v>-9.415293534722437</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.332746418223508</v>
       </c>
       <c r="E68">
-        <v>-11.62214494995926</v>
+        <v>-12.38130738955313</v>
       </c>
       <c r="F68">
-        <v>-1.159731906882274</v>
+        <v>-0.6812668950252799</v>
       </c>
       <c r="G68">
-        <v>-8.745520746343903</v>
+        <v>-8.999027924026601</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.412884747193374</v>
       </c>
       <c r="E69">
-        <v>-11.61536129589577</v>
+        <v>-13.03437674009531</v>
       </c>
       <c r="F69">
-        <v>-1.199305502816215</v>
+        <v>-0.9204248478875252</v>
       </c>
       <c r="G69">
-        <v>-8.573830828245958</v>
+        <v>-10.17702583852597</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.473387256001727</v>
       </c>
       <c r="E70">
-        <v>-12.09442856116722</v>
+        <v>-13.89469623207252</v>
       </c>
       <c r="F70">
-        <v>-1.443320173761074</v>
+        <v>-1.531412905211787</v>
       </c>
       <c r="G70">
-        <v>-8.549503851604236</v>
+        <v>-9.815888031250363</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.508869522629346</v>
       </c>
       <c r="E71">
-        <v>-12.47338032307709</v>
+        <v>-13.72706570973059</v>
       </c>
       <c r="F71">
-        <v>-1.534341183980684</v>
+        <v>-0.9082751831906649</v>
       </c>
       <c r="G71">
-        <v>-9.588213910905173</v>
+        <v>-9.606618282632098</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.516917336677543</v>
       </c>
       <c r="E72">
-        <v>-12.68732354909547</v>
+        <v>-13.37617690124625</v>
       </c>
       <c r="F72">
-        <v>-1.632967435325396</v>
+        <v>-1.742964686008336</v>
       </c>
       <c r="G72">
-        <v>-8.213418170934991</v>
+        <v>-8.775960638750872</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.49529682097338</v>
       </c>
       <c r="E73">
-        <v>-12.41121343189979</v>
+        <v>-14.09386757587788</v>
       </c>
       <c r="F73">
-        <v>-1.788440399687224</v>
+        <v>-1.124300147962331</v>
       </c>
       <c r="G73">
-        <v>-8.585091980637973</v>
+        <v>-9.857461108408529</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.442457374569726</v>
       </c>
       <c r="E74">
-        <v>-12.75943496919361</v>
+        <v>-13.5409861842814</v>
       </c>
       <c r="F74">
-        <v>-1.396140508334628</v>
+        <v>-1.068802017076973</v>
       </c>
       <c r="G74">
-        <v>-8.050961610305324</v>
+        <v>-8.663329427501372</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.359809678348643</v>
       </c>
       <c r="E75">
-        <v>-12.4823014168722</v>
+        <v>-14.46895654945921</v>
       </c>
       <c r="F75">
-        <v>-1.396837165320383</v>
+        <v>-1.181955347564579</v>
       </c>
       <c r="G75">
-        <v>-7.940512411392855</v>
+        <v>-7.815022092851892</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.247569483312388</v>
       </c>
       <c r="E76">
-        <v>-13.03600699073807</v>
+        <v>-14.2386428899031</v>
       </c>
       <c r="F76">
-        <v>-1.904672771811036</v>
+        <v>-1.475176698970535</v>
       </c>
       <c r="G76">
-        <v>-7.05158355383745</v>
+        <v>-9.161428703889758</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.110653992269046</v>
       </c>
       <c r="E77">
-        <v>-13.14310540101947</v>
+        <v>-13.96256447202548</v>
       </c>
       <c r="F77">
-        <v>-1.465644675266521</v>
+        <v>-1.793905139443492</v>
       </c>
       <c r="G77">
-        <v>-7.251728225298899</v>
+        <v>-7.777491480654963</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.950902240787795</v>
       </c>
       <c r="E78">
-        <v>-12.87421367139202</v>
+        <v>-15.05768081282639</v>
       </c>
       <c r="F78">
-        <v>-1.943446993201275</v>
+        <v>-1.102093274628082</v>
       </c>
       <c r="G78">
-        <v>-6.672008562619325</v>
+        <v>-8.120411945832531</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.775325302387118</v>
       </c>
       <c r="E79">
-        <v>-13.39460779045747</v>
+        <v>-14.60149139824169</v>
       </c>
       <c r="F79">
-        <v>-1.858494602574575</v>
+        <v>-1.633209318607013</v>
       </c>
       <c r="G79">
-        <v>-6.383569500214779</v>
+        <v>-7.969045914073787</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.586271623638756</v>
       </c>
       <c r="E80">
-        <v>-13.96710653145517</v>
+        <v>-14.28325741582667</v>
       </c>
       <c r="F80">
-        <v>-1.596017278956121</v>
+        <v>-1.737026120097667</v>
       </c>
       <c r="G80">
-        <v>-6.226684453793048</v>
+        <v>-7.476928304588268</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.390827268121543</v>
       </c>
       <c r="E81">
-        <v>-15.58148487281961</v>
+        <v>-15.60732887398139</v>
       </c>
       <c r="F81">
-        <v>-1.886421352825155</v>
+        <v>-1.948334360877793</v>
       </c>
       <c r="G81">
-        <v>-5.874514225039406</v>
+        <v>-5.548944859468182</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.191319349445943</v>
       </c>
       <c r="E82">
-        <v>-14.3871270241406</v>
+        <v>-14.59868374435694</v>
       </c>
       <c r="F82">
-        <v>-1.910940199580617</v>
+        <v>-1.983000708317549</v>
       </c>
       <c r="G82">
-        <v>-5.891642201579708</v>
+        <v>-6.829159387987371</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.994663115340768</v>
       </c>
       <c r="E83">
-        <v>-15.41869528919188</v>
+        <v>-17.78854989230796</v>
       </c>
       <c r="F83">
-        <v>-2.236150614980481</v>
+        <v>-2.091476248081547</v>
       </c>
       <c r="G83">
-        <v>-4.961094329764305</v>
+        <v>-6.458971971650818</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.803221562695316</v>
       </c>
       <c r="E84">
-        <v>-16.78440153737312</v>
+        <v>-19.33163646736964</v>
       </c>
       <c r="F84">
-        <v>-2.425560963467602</v>
+        <v>-2.173806855878387</v>
       </c>
       <c r="G84">
-        <v>-5.185418322897302</v>
+        <v>-6.60946519847475</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.623043055305578</v>
       </c>
       <c r="E85">
-        <v>-18.25454798159327</v>
+        <v>-18.90430248916183</v>
       </c>
       <c r="F85">
-        <v>-2.597728844465451</v>
+        <v>-2.0489122458235</v>
       </c>
       <c r="G85">
-        <v>-4.808425653046461</v>
+        <v>-5.687025225132735</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.456549204513762</v>
       </c>
       <c r="E86">
-        <v>-18.87904266114704</v>
+        <v>-19.37278218220334</v>
       </c>
       <c r="F86">
-        <v>-2.478800964812929</v>
+        <v>-1.973409870527936</v>
       </c>
       <c r="G86">
-        <v>-4.764857593180154</v>
+        <v>-5.587125153533881</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.308955995900722</v>
       </c>
       <c r="E87">
-        <v>-19.46942887447504</v>
+        <v>-20.22183030237546</v>
       </c>
       <c r="F87">
-        <v>-2.575854974827127</v>
+        <v>-2.317399374949265</v>
       </c>
       <c r="G87">
-        <v>-4.275312461397241</v>
+        <v>-5.31620125181365</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.182659550412387</v>
       </c>
       <c r="E88">
-        <v>-20.4498027408696</v>
+        <v>-22.27771674559173</v>
       </c>
       <c r="F88">
-        <v>-2.835293846812113</v>
+        <v>-1.705138945294302</v>
       </c>
       <c r="G88">
-        <v>-4.579206077346773</v>
+        <v>-5.999285956058851</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.081986053716958</v>
       </c>
       <c r="E89">
-        <v>-22.19918394935072</v>
+        <v>-22.69436352514145</v>
       </c>
       <c r="F89">
-        <v>-2.600872498759075</v>
+        <v>-2.640090725077215</v>
       </c>
       <c r="G89">
-        <v>-4.412716895420547</v>
+        <v>-5.569708429496349</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.008982309689562</v>
       </c>
       <c r="E90">
-        <v>-23.8454699185732</v>
+        <v>-24.44374473362257</v>
       </c>
       <c r="F90">
-        <v>-2.877399761896412</v>
+        <v>-2.936253609130511</v>
       </c>
       <c r="G90">
-        <v>-4.100987722387062</v>
+        <v>-4.583698069661652</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.967229743849058</v>
       </c>
       <c r="E91">
-        <v>-25.52898447261275</v>
+        <v>-26.65923724323918</v>
       </c>
       <c r="F91">
-        <v>-3.104789099067085</v>
+        <v>-2.902994657908111</v>
       </c>
       <c r="G91">
-        <v>-4.11376151791798</v>
+        <v>-4.301444109896658</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.958991997273601</v>
       </c>
       <c r="E92">
-        <v>-27.02267898167278</v>
+        <v>-27.45878008555945</v>
       </c>
       <c r="F92">
-        <v>-3.479381808817438</v>
+        <v>-2.26218951592008</v>
       </c>
       <c r="G92">
-        <v>-4.615247014955713</v>
+        <v>-5.43237290112579</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.987877731097914</v>
       </c>
       <c r="E93">
-        <v>-29.20203879718219</v>
+        <v>-29.41974065662694</v>
       </c>
       <c r="F93">
-        <v>-3.244972886275442</v>
+        <v>-2.652060634047668</v>
       </c>
       <c r="G93">
-        <v>-4.108052192404546</v>
+        <v>-5.613821172141524</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.056393567474447</v>
       </c>
       <c r="E94">
-        <v>-30.35794537306208</v>
+        <v>-30.67572877231334</v>
       </c>
       <c r="F94">
-        <v>-3.656131389920171</v>
+        <v>-3.311349137894363</v>
       </c>
       <c r="G94">
-        <v>-4.305798290906042</v>
+        <v>-5.844615734189746</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.166085145276859</v>
       </c>
       <c r="E95">
-        <v>-32.32117697384441</v>
+        <v>-33.127401579563</v>
       </c>
       <c r="F95">
-        <v>-3.686051192141886</v>
+        <v>-3.252106786348351</v>
       </c>
       <c r="G95">
-        <v>-5.289508514427567</v>
+        <v>-5.747481732365504</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.317576494526792</v>
       </c>
       <c r="E96">
-        <v>-34.22946007101767</v>
+        <v>-36.16586725601557</v>
       </c>
       <c r="F96">
-        <v>-3.98724060959537</v>
+        <v>-3.26678877019557</v>
       </c>
       <c r="G96">
-        <v>-5.103834030043269</v>
+        <v>-5.868473496148469</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.504336746651136</v>
       </c>
       <c r="E97">
-        <v>-37.3461845710338</v>
+        <v>-39.72960648227685</v>
       </c>
       <c r="F97">
-        <v>-4.164926245863266</v>
+        <v>-3.224165953851924</v>
       </c>
       <c r="G97">
-        <v>-5.665457755822505</v>
+        <v>-6.460008837663603</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.721622871711131</v>
       </c>
       <c r="E98">
-        <v>-38.79917941994989</v>
+        <v>-39.49718255383317</v>
       </c>
       <c r="F98">
-        <v>-3.991926683993007</v>
+        <v>-3.705908815521796</v>
       </c>
       <c r="G98">
-        <v>-5.776655073250527</v>
+        <v>-6.08426303200535</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.949324919324443</v>
       </c>
       <c r="E99">
-        <v>-41.27098808687465</v>
+        <v>-43.0228078786089</v>
       </c>
       <c r="F99">
-        <v>-4.38268415524159</v>
+        <v>-3.744132172589174</v>
       </c>
       <c r="G99">
-        <v>-6.629739866490558</v>
+        <v>-6.847977193630786</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.18062563212599</v>
       </c>
       <c r="E100">
-        <v>-43.62316352746478</v>
+        <v>-45.05094383310617</v>
       </c>
       <c r="F100">
-        <v>-4.322372381378563</v>
+        <v>-3.850941037138739</v>
       </c>
       <c r="G100">
-        <v>-7.071382444727139</v>
+        <v>-6.035819076901708</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.380287769291836</v>
       </c>
       <c r="E101">
-        <v>-45.69692159335233</v>
+        <v>-47.07010888059424</v>
       </c>
       <c r="F101">
-        <v>-4.209972865227503</v>
+        <v>-4.105696319828296</v>
       </c>
       <c r="G101">
-        <v>-7.249277152793994</v>
+        <v>-7.235062900998479</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.554073509763398</v>
       </c>
       <c r="E102">
-        <v>-48.91275174702632</v>
+        <v>-49.7744660089979</v>
       </c>
       <c r="F102">
-        <v>-4.545115405786933</v>
+        <v>-4.064524803174355</v>
       </c>
       <c r="G102">
-        <v>-7.403645502279629</v>
+        <v>-6.955030328229229</v>
       </c>
     </row>
   </sheetData>
